--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6606.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6606.xlsx
@@ -821,9 +821,21 @@
       <c r="G6" t="n">
         <v>0.87</v>
       </c>
+      <c r="H6" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6879999999999999</v>
+      </c>
       <c r="K6" t="n">
         <v>0.5620000000000001</v>
       </c>
+      <c r="L6" t="n">
+        <v>0.297</v>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>6606-06-06-06-FG</t>
@@ -831,17 +843,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: M10_1@DRIVE, M10_2@DRIVE, M10_3@DRIVE, M5_1@DRIVE, M5_2@DRIVE, M5_3@DRIVE, Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6606-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: M10_1@DRIVE, M10_2@DRIVE, M10_3@DRIVE, M5_1@DRIVE, M5_2@DRIVE, M5_3@DRIVE, Y@HEX, C3_1HEX@HEX, C3_2HEX@HEX, C3_3HEX@HEX, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6606-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6606-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6606-06-06-06-FG (PARTcommunity / CADENAS, M10_1@DRIVE=M, M10_2@DRIVE=M, M10_3@DRIVE=M, M5_1@DRIVE=M6, M5_2@DRIVE=M6, M5_3@DRIVE=M6, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6606-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6606-06-06-06-FG (PARTcommunity / CADENAS, M10_1@DRIVE=M, M10_2@DRIVE=M, M10_3@DRIVE=M, M5_1@DRIVE=M6, M5_2@DRIVE=M6, M5_3@DRIVE=M6, Y@HEX=Y, C3_1HEX@HEX=C, C3_2HEX@HEX=C, C3_3HEX@HEX=C, D1@BORE=A1D; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1062,9 +1074,21 @@
       <c r="G9" t="n">
         <v>1.18</v>
       </c>
+      <c r="H9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.25</v>
+      </c>
       <c r="K9" t="n">
         <v>1.062</v>
       </c>
+      <c r="L9" t="n">
+        <v>0.609</v>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>6606-12-12-12-FG</t>
@@ -1072,17 +1096,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: M10_1@DRIVE, M10_2@DRIVE, M10_3@DRIVE, M5_1@DRIVE, M5_2@DRIVE, M5_3@DRIVE, Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6606-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: M10_1@DRIVE, M10_2@DRIVE, M10_3@DRIVE, M5_1@DRIVE, M5_2@DRIVE, M5_3@DRIVE, Y@HEX, C3_1HEX@HEX, C3_2HEX@HEX, C3_3HEX@HEX, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6606-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6606-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6606-12-12-12-FG (PARTcommunity / CADENAS, M10_1@DRIVE=M, M10_2@DRIVE=M, M10_3@DRIVE=M, M5_1@DRIVE=M6, M5_2@DRIVE=M6, M5_3@DRIVE=M6, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6606-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6606-12-12-12-FG (PARTcommunity / CADENAS, M10_1@DRIVE=M, M10_2@DRIVE=M, M10_3@DRIVE=M, M5_1@DRIVE=M6, M5_2@DRIVE=M6, M5_3@DRIVE=M6, Y@HEX=Y, C3_1HEX@HEX=C, C3_2HEX@HEX=C, C3_3HEX@HEX=C, D1@BORE=A1D; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
